--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4044,6 +4044,236 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118843560</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90017</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686857</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6560564</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118843561</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90017</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686867</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6560589</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -4046,7 +4046,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118843560</v>
+        <v>118843561</v>
       </c>
       <c r="B30" t="n">
         <v>90017</v>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686857</v>
+        <v>686867</v>
       </c>
       <c r="R30" t="n">
-        <v>6560564</v>
+        <v>6560589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
+          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4161,7 +4161,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118843561</v>
+        <v>118843560</v>
       </c>
       <c r="B31" t="n">
         <v>90017</v>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686867</v>
+        <v>686857</v>
       </c>
       <c r="R31" t="n">
-        <v>6560589</v>
+        <v>6560564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
+          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -4046,7 +4046,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118843561</v>
+        <v>118843560</v>
       </c>
       <c r="B30" t="n">
         <v>90017</v>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686867</v>
+        <v>686857</v>
       </c>
       <c r="R30" t="n">
-        <v>6560589</v>
+        <v>6560564</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
+          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4161,7 +4161,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118843560</v>
+        <v>118843561</v>
       </c>
       <c r="B31" t="n">
         <v>90017</v>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686857</v>
+        <v>686867</v>
       </c>
       <c r="R31" t="n">
-        <v>6560564</v>
+        <v>6560589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
+          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -4049,7 +4049,7 @@
         <v>118843560</v>
       </c>
       <c r="B30" t="n">
-        <v>90017</v>
+        <v>90024</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>118843561</v>
       </c>
       <c r="B31" t="n">
-        <v>90017</v>
+        <v>90024</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95221262</v>
+        <v>96405624</v>
       </c>
       <c r="B2" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686795.0104412795</v>
+        <v>686898</v>
       </c>
       <c r="R2" t="n">
-        <v>6560637.484459142</v>
+        <v>6560571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,42 +776,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95913006</v>
+        <v>100752319</v>
       </c>
       <c r="B3" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686974.3093199586</v>
+        <v>686811</v>
       </c>
       <c r="R3" t="n">
-        <v>6560760.350246437</v>
+        <v>6560622</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,56 +886,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96406248</v>
+        <v>113700091</v>
       </c>
       <c r="B4" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686898.6205370232</v>
+        <v>686783</v>
       </c>
       <c r="R4" t="n">
-        <v>6560571.645622306</v>
+        <v>6560605</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +965,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Samtliga fyra kaplslar var unga kapslar som vuxit upp i år. Det fanns även ett gammalt kapselskaft där kapseln fallit av.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,56 +994,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96405624</v>
+        <v>95913006</v>
       </c>
       <c r="B5" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686897.643662005</v>
+        <v>686974</v>
       </c>
       <c r="R5" t="n">
-        <v>6560570.569975963</v>
+        <v>6560760</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,22 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,43 +1133,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96703967</v>
+        <v>111770854</v>
       </c>
       <c r="B6" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686873.4028637917</v>
+        <v>687560</v>
       </c>
       <c r="R6" t="n">
-        <v>6560592.506770783</v>
+        <v>6560820</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,51 +1234,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100752319</v>
+        <v>109395707</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686810.7071133712</v>
+        <v>687473</v>
       </c>
       <c r="R7" t="n">
-        <v>6560621.809349775</v>
+        <v>6560950</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,22 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,44 +1335,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100752196</v>
+        <v>111771509</v>
       </c>
       <c r="B8" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4189</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1428,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686874.7343183032</v>
+        <v>687351</v>
       </c>
       <c r="R8" t="n">
-        <v>6560565.336187014</v>
+        <v>6560835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,22 +1403,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I sluttning med äldre barrblandskog. Curry/buljongdoft.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,15 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100752361</v>
+        <v>113660887</v>
       </c>
       <c r="B9" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,30 +1452,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4189</v>
+        <v>2609</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1548,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686895.2346763669</v>
+        <v>686758</v>
       </c>
       <c r="R9" t="n">
-        <v>6560598.715486779</v>
+        <v>6560670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,22 +1510,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ihop med rävsvansmossa under överhäng.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,27 +1536,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101855762</v>
+        <v>113700088</v>
       </c>
       <c r="B10" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,38 +1559,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686793.9493352512</v>
+        <v>686769</v>
       </c>
       <c r="R10" t="n">
-        <v>6560606.599886982</v>
+        <v>6560673</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,22 +1613,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,34 +1637,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Nära basen av lodvägg.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101855727</v>
+        <v>113700085</v>
       </c>
       <c r="B11" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,47 +1671,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686767.1325044284</v>
+        <v>686998</v>
       </c>
       <c r="R11" t="n">
-        <v>6560597.064349053</v>
+        <v>6560738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,22 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,72 +1749,68 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101855822</v>
+        <v>113700090</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687459.8782059408</v>
+        <v>686783</v>
       </c>
       <c r="R12" t="n">
-        <v>6560778.537605848</v>
+        <v>6560605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,27 +1837,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grenar på levande gran som växer ganska högt upp i en nordbrant.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,34 +1861,48 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101855771</v>
+        <v>100752196</v>
       </c>
       <c r="B13" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,27 +1910,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2029,13 +1941,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687230.9115832971</v>
+        <v>686875</v>
       </c>
       <c r="R13" t="n">
-        <v>6560786.815155534</v>
+        <v>6560565</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,22 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,40 +2004,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109395707</v>
+        <v>100752361</v>
       </c>
       <c r="B14" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>4189</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2145,13 +2046,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687473.0791247347</v>
+        <v>686895</v>
       </c>
       <c r="R14" t="n">
-        <v>6560949.786377818</v>
+        <v>6560599</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,22 +2076,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,44 +2109,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111751995</v>
+        <v>111770759</v>
       </c>
       <c r="B15" t="n">
-        <v>90021</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2265,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686835</v>
+        <v>687356</v>
       </c>
       <c r="R15" t="n">
-        <v>6560679</v>
+        <v>6560761</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,12 +2177,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,15 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111770759</v>
+        <v>111770541</v>
       </c>
       <c r="B16" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2371,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687356</v>
+        <v>686901</v>
       </c>
       <c r="R16" t="n">
-        <v>6560761</v>
+        <v>6560554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2434,15 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111770854</v>
+        <v>95221262</v>
       </c>
       <c r="B17" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,21 +2322,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4368</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,13 +2349,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687560</v>
+        <v>686795</v>
       </c>
       <c r="R17" t="n">
-        <v>6560820</v>
+        <v>6560637</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,12 +2379,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,15 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111771509</v>
+        <v>96406248</v>
       </c>
       <c r="B18" t="n">
-        <v>91590</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>4368</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2583,13 +2450,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687351</v>
+        <v>686899</v>
       </c>
       <c r="R18" t="n">
-        <v>6560835</v>
+        <v>6560572</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2613,17 +2480,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I sluttning med äldre barrblandskog. Curry/buljongdoft.</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,15 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113660887</v>
+        <v>113700083</v>
       </c>
       <c r="B19" t="n">
-        <v>96305</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,27 +2524,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2609</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2695,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686758</v>
+        <v>687087</v>
       </c>
       <c r="R19" t="n">
-        <v>6560670</v>
+        <v>6560772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,14 +2584,19 @@
           <t>2023-12-17</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-12-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ihop med rävsvansmossa under överhäng.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,82 +2609,86 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Stående död klen asp med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula # Stående död klen asp med barken kvar.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113700091</v>
+        <v>92152986</v>
       </c>
       <c r="B20" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686783</v>
+        <v>687425</v>
       </c>
       <c r="R20" t="n">
-        <v>6560605</v>
+        <v>6560743</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2847,27 +2712,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Samtliga fyra kaplslar var unga kapslar som vuxit upp i år. Det fanns även ett gammalt kapselskaft där kapseln fallit av.</t>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,96 +2731,74 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113700090</v>
+        <v>96704254</v>
       </c>
       <c r="B21" t="n">
-        <v>94179</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>5445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686783</v>
+        <v>686951</v>
       </c>
       <c r="R21" t="n">
-        <v>6560605</v>
+        <v>6560777</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,22 +2822,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-10-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer på en liten senvuxen ek.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,88 +2841,67 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113700087</v>
+        <v>111751303</v>
       </c>
       <c r="B22" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>5741</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686920</v>
+        <v>686857</v>
       </c>
       <c r="R22" t="n">
-        <v>6560685</v>
+        <v>6560564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3121,22 +2928,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Prov 19.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3145,68 +2947,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113700085</v>
+        <v>118843561</v>
       </c>
       <c r="B23" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>5741</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686998</v>
+        <v>686867</v>
       </c>
       <c r="R23" t="n">
-        <v>6560738</v>
+        <v>6560589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,22 +3034,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3257,33 +3053,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113700083</v>
+        <v>111751995</v>
       </c>
       <c r="B24" t="n">
-        <v>90316</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3291,24 +3087,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3318,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687087</v>
+        <v>686835</v>
       </c>
       <c r="R24" t="n">
-        <v>6560772</v>
+        <v>6560679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3348,22 +3148,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,85 +3166,63 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Stående död klen asp med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula # Stående död klen asp med barken kvar.</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113700088</v>
+        <v>98583597</v>
       </c>
       <c r="B25" t="n">
-        <v>94158</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686769</v>
+        <v>687001</v>
       </c>
       <c r="R25" t="n">
-        <v>6560673</v>
+        <v>6560692</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,22 +3249,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2022-02-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Några meter upp på tallstam.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,38 +3268,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Nära basen av lodvägg.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113700082</v>
+        <v>113700084</v>
       </c>
       <c r="B26" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3544,27 +3298,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3573,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687128</v>
+        <v>687018</v>
       </c>
       <c r="R26" t="n">
-        <v>6560770</v>
+        <v>6560740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3608,7 +3362,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3372,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska födosökshack 1,5 meter  upp på stående död gran. Det låg hackspån ovanpå snön, så spåren kan inte ha varit mer än några dagar gamla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,26 +3388,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Barklös tallåga.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Barklös tallåga.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3665,32 +3404,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113700084</v>
+        <v>126528490</v>
       </c>
       <c r="B27" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3699,24 +3433,23 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687018</v>
+        <v>687519</v>
       </c>
       <c r="R27" t="n">
-        <v>6560740</v>
+        <v>6560832</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3740,27 +3473,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska födosökshack 1,5 meter  upp på stående död gran. Det låg hackspån ovanpå snön, så spåren kan inte ha varit mer än några dagar gamla.</t>
+          <t>Satt i ett träd på ett hygge.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3775,27 +3498,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113700089</v>
+        <v>113700081</v>
       </c>
       <c r="B28" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3803,27 +3521,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3832,10 +3550,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686791</v>
+        <v>687141</v>
       </c>
       <c r="R28" t="n">
-        <v>6560629</v>
+        <v>6560765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3867,7 +3585,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3877,7 +3595,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Stora mängder spillning ovanpå snön.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3888,26 +3611,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>20 cm tjock granlåga med merparten av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # 20 cm tjock granlåga med merparten av barken kvar.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3924,15 +3627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113700081</v>
+        <v>115893087</v>
       </c>
       <c r="B29" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3958,21 +3656,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerskogen, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687141</v>
+        <v>686991</v>
       </c>
       <c r="R29" t="n">
-        <v>6560765</v>
+        <v>6560713</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3999,27 +3700,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Stora mängder spillning ovanpå snön.</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4034,27 +3730,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Johan Skutin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Johan Skutin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118843560</v>
+        <v>115893307</v>
       </c>
       <c r="B30" t="n">
-        <v>90026</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4062,26 +3753,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5741</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4089,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686857</v>
+        <v>687100</v>
       </c>
       <c r="R30" t="n">
-        <v>6560564</v>
+        <v>6560742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4119,17 +3815,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kollekt BR19. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751303</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4138,38 +3839,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Skutin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118843561</v>
+        <v>115893318</v>
       </c>
       <c r="B31" t="n">
-        <v>90026</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4177,26 +3868,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5741</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4204,10 +3900,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686867</v>
+        <v>687146</v>
       </c>
       <c r="R31" t="n">
-        <v>6560589</v>
+        <v>6560746</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4234,17 +3930,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Kollekt BR18. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/111751239</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4253,61 +3954,60 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Skutin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126528490</v>
+        <v>115893325</v>
       </c>
       <c r="B32" t="n">
-        <v>57603</v>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100067</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4315,13 +4015,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687519</v>
+        <v>687130</v>
       </c>
       <c r="R32" t="n">
-        <v>6560832</v>
+        <v>6560728</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4345,17 +4045,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Satt i ett träd på ett hygge.</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4370,15 +4075,905 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Skutin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>113700089</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>686791</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6560629</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>20 cm tjock granlåga med merparten av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # 20 cm tjock granlåga med merparten av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>113700082</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687128</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6560770</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Barklös tallåga.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Barklös tallåga.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>101855727</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>686767</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6560597</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>101855762</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>686794</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6560607</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>101855771</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687231</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6560787</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>100752648</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>686779</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6560605</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>96703967</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>686873</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6560593</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>113700087</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västerskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>686920</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6560685</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60204-2023 artfynd.xlsx
+++ b/artfynd/A 60204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96405624</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100752319</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95913006</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111770854</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109395707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111771509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113660887</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700088</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700085</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700090</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100752196</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2106,6 +2171,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100752361</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2207,6 +2277,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111770759</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2308,6 +2383,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111770541</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95221262</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96406248</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,6 +2731,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700083</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2747,6 +2842,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92152986</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96704254</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2963,6 +3068,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111751303</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3073,6 +3183,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843561</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3178,6 +3293,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111751995</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3284,6 +3404,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98583597</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3401,6 +3526,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700084</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3507,6 +3637,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126528490</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3624,6 +3759,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700081</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3739,6 +3879,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115893087</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3854,6 +3999,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115893307</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3969,6 +4119,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115893318</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4084,6 +4239,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115893325</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4216,6 +4376,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700089</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4348,6 +4513,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700082</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4459,6 +4629,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101855727</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4561,6 +4736,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101855762</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4663,6 +4843,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101855771</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4765,6 +4950,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100752648</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4867,6 +5057,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96703967</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4974,8 +5169,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113700087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>